--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danth\Documents\DATA309\Datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01541BC-D40A-4125-B2A9-462EE2489835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800BBA93-AF15-4166-A64F-C05BE77FF71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4630" yWindow="1700" windowWidth="16920" windowHeight="10450" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
+    <workbookView xWindow="5310" yWindow="2380" windowWidth="16920" windowHeight="10450" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Dataset</t>
   </si>
@@ -47,22 +47,58 @@
     <t>Source</t>
   </si>
   <si>
-    <t>CCC Property Values</t>
-  </si>
-  <si>
-    <t>CCC Property Locations</t>
-  </si>
-  <si>
     <t>https://catalogue.data.govt.nz/dataset/rating-unit-opendata3/resource/2afdfb0a-1c50-4ebc-aaaa-a6b3f25f6ddd</t>
   </si>
   <si>
     <t>https://catalogue.data.govt.nz/dataset/vdh-current-rating-unit-value-opendata1/resource/e0b25ad3-1fd1-42a9-9094-e159942c6c63</t>
   </si>
   <si>
-    <t>ECAN Property Values</t>
-  </si>
-  <si>
     <t>https://catalogue.data.govt.nz/dataset/rating-units4/resource/01dd11fb-bb71-47c6-a5e0-11e949094a77</t>
+  </si>
+  <si>
+    <t>Opes_Partners</t>
+  </si>
+  <si>
+    <t>https://www.opespartners.co.nz/property-markets/canterbury</t>
+  </si>
+  <si>
+    <t>National_Properties</t>
+  </si>
+  <si>
+    <t>https://data.linz.govt.nz/table/114085-nz-properties-national-district-valuation-roll/</t>
+  </si>
+  <si>
+    <t>CCC Property Values (Canterbury_Properties)</t>
+  </si>
+  <si>
+    <t>CCC Property Locations (Canterbury_Properties)</t>
+  </si>
+  <si>
+    <t>ECAN Property Values (Canterbury_Properties)</t>
+  </si>
+  <si>
+    <t>Quarterly New Dwelling Consent Analysis Canterbury</t>
+  </si>
+  <si>
+    <t>Quarterly New Dwelling Consent Analysis NZ</t>
+  </si>
+  <si>
+    <t>https://www.interest.co.nz/property/residential-building-consent-analysis-canterbury</t>
+  </si>
+  <si>
+    <t>https://www.interest.co.nz/property/residential-building-consent-analysis</t>
+  </si>
+  <si>
+    <t>household-income-and-housing-cost-statistics</t>
+  </si>
+  <si>
+    <t>https://www.stats.govt.nz/information-releases/household-income-and-housing-cost-statistics-year-ended-june-2025/</t>
+  </si>
+  <si>
+    <t>QV_House_Price_Index</t>
+  </si>
+  <si>
+    <t>https://www.qv.co.nz/price-index/</t>
   </si>
 </sst>
 </file>
@@ -445,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061C0C33-7D3C-4AAD-B222-7BF2650F4FDB}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.7265625" customWidth="1"/>
@@ -461,26 +497,74 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -488,6 +572,12 @@
     <hyperlink ref="B3" r:id="rId1" xr:uid="{80920613-ABD1-41C7-A274-B2FA9B48C0E0}"/>
     <hyperlink ref="B2" r:id="rId2" xr:uid="{CB372C96-0B73-4A51-A9FE-A965996981D2}"/>
     <hyperlink ref="B4" r:id="rId3" xr:uid="{743C70B2-0BE7-4E52-A782-F4A2C8CE0CFF}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{D9716AD7-B15C-49CE-B9CF-2D9C0FF38769}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{57B978B8-B551-4CF0-95A4-DB6556C3CDF4}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{E0A6EC95-0230-4D9E-8C2C-C46096AE3BD1}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{38680BAB-D2B4-4206-92EB-FD27E6076FB8}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{EE6C9D94-14BB-4174-9569-2B379E9F2A58}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{A64392DD-F1D0-4487-AC77-534D20F3FAE3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
